--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/162.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/162.xlsx
@@ -426,13 +426,13 @@
         <v>-6.530344111342651</v>
       </c>
       <c r="E2">
-        <v>-3.337378736984471</v>
+        <v>-5.034668908955352</v>
       </c>
       <c r="F2">
-        <v>-3.985414001997769</v>
+        <v>-3.805439286208357</v>
       </c>
       <c r="G2">
-        <v>-11.37032471730175</v>
+        <v>-11.8578753799613</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.384799807582539</v>
       </c>
       <c r="E3">
-        <v>-4.404740060592375</v>
+        <v>-4.819344498364634</v>
       </c>
       <c r="F3">
-        <v>-3.580093771500478</v>
+        <v>-4.422821698047779</v>
       </c>
       <c r="G3">
-        <v>-11.40149681409953</v>
+        <v>-12.27148500800122</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.300722687186574</v>
       </c>
       <c r="E4">
-        <v>-4.359627402527963</v>
+        <v>-6.338443746607694</v>
       </c>
       <c r="F4">
-        <v>-3.49341279563073</v>
+        <v>-3.792068849017259</v>
       </c>
       <c r="G4">
-        <v>-11.0585971282329</v>
+        <v>-11.53663659355812</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.285519460311212</v>
       </c>
       <c r="E5">
-        <v>-4.864724336395499</v>
+        <v>-5.434175414386039</v>
       </c>
       <c r="F5">
-        <v>-3.543870457949589</v>
+        <v>-3.679719167670069</v>
       </c>
       <c r="G5">
-        <v>-10.99752418412442</v>
+        <v>-11.30214072137492</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.301068643417789</v>
       </c>
       <c r="E6">
-        <v>-6.007371540380921</v>
+        <v>-7.538362561368124</v>
       </c>
       <c r="F6">
-        <v>-3.215627610650821</v>
+        <v>-3.736411088325055</v>
       </c>
       <c r="G6">
-        <v>-10.24995665371944</v>
+        <v>-10.95965816424624</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.310331280113219</v>
       </c>
       <c r="E7">
-        <v>-6.089051626057272</v>
+        <v>-7.873360954559546</v>
       </c>
       <c r="F7">
-        <v>-3.400402539069929</v>
+        <v>-3.889054999278771</v>
       </c>
       <c r="G7">
-        <v>-10.54160578409261</v>
+        <v>-11.02577637975656</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.267970854637507</v>
       </c>
       <c r="E8">
-        <v>-6.095513758466217</v>
+        <v>-9.445656186970711</v>
       </c>
       <c r="F8">
-        <v>-3.375042656245998</v>
+        <v>-3.698618322211966</v>
       </c>
       <c r="G8">
-        <v>-9.864983244594209</v>
+        <v>-11.16404131420422</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.134570856179481</v>
       </c>
       <c r="E9">
-        <v>-7.059141327980416</v>
+        <v>-8.405556276888982</v>
       </c>
       <c r="F9">
-        <v>-2.955038304500752</v>
+        <v>-3.214919694106619</v>
       </c>
       <c r="G9">
-        <v>-9.872915311706302</v>
+        <v>-9.351501078725551</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.881604725161146</v>
       </c>
       <c r="E10">
-        <v>-8.101016399873151</v>
+        <v>-9.107275023695557</v>
       </c>
       <c r="F10">
-        <v>-2.928311683471796</v>
+        <v>-3.414583833689732</v>
       </c>
       <c r="G10">
-        <v>-10.4604411391063</v>
+        <v>-9.516518531676063</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.499154964218614</v>
       </c>
       <c r="E11">
-        <v>-9.46709851139703</v>
+        <v>-10.19633226627421</v>
       </c>
       <c r="F11">
-        <v>-2.900628504069914</v>
+        <v>-3.315183323760133</v>
       </c>
       <c r="G11">
-        <v>-9.680761316970385</v>
+        <v>-9.554593115923222</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.998460396737163</v>
       </c>
       <c r="E12">
-        <v>-8.953845795841678</v>
+        <v>-10.82915028105408</v>
       </c>
       <c r="F12">
-        <v>-2.85214889043944</v>
+        <v>-3.091016878106299</v>
       </c>
       <c r="G12">
-        <v>-8.858584021746847</v>
+        <v>-9.527324152316245</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.411955879848355</v>
       </c>
       <c r="E13">
-        <v>-10.0577654901135</v>
+        <v>-11.37575973614993</v>
       </c>
       <c r="F13">
-        <v>-2.28864019457848</v>
+        <v>-2.996922574846379</v>
       </c>
       <c r="G13">
-        <v>-9.213017648272299</v>
+        <v>-9.558635292026672</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.794776756443704</v>
       </c>
       <c r="E14">
-        <v>-12.02072311821837</v>
+        <v>-13.10821350879037</v>
       </c>
       <c r="F14">
-        <v>-2.287112710223038</v>
+        <v>-2.667611517907647</v>
       </c>
       <c r="G14">
-        <v>-9.189055919659054</v>
+        <v>-9.225985055149623</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.210785452934032</v>
       </c>
       <c r="E15">
-        <v>-12.12137750998686</v>
+        <v>-11.75994188553866</v>
       </c>
       <c r="F15">
-        <v>-2.104805987473142</v>
+        <v>-2.771759186318776</v>
       </c>
       <c r="G15">
-        <v>-8.58275598850585</v>
+        <v>-8.937543843404004</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.720794067330336</v>
       </c>
       <c r="E16">
-        <v>-12.84403592060491</v>
+        <v>-13.74822274029442</v>
       </c>
       <c r="F16">
-        <v>-1.80367143432895</v>
+        <v>-2.347989573759573</v>
       </c>
       <c r="G16">
-        <v>-8.118706888629589</v>
+        <v>-8.498231139797179</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.375295655871338</v>
       </c>
       <c r="E17">
-        <v>-13.16731009459047</v>
+        <v>-14.85633127302335</v>
       </c>
       <c r="F17">
-        <v>-1.735419252344214</v>
+        <v>-2.335591532000555</v>
       </c>
       <c r="G17">
-        <v>-8.115548628185126</v>
+        <v>-8.114601812160894</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.206003877455556</v>
       </c>
       <c r="E18">
-        <v>-13.90828618256954</v>
+        <v>-15.70461860956218</v>
       </c>
       <c r="F18">
-        <v>-1.417277281374118</v>
+        <v>-2.094325021724763</v>
       </c>
       <c r="G18">
-        <v>-6.960585363717429</v>
+        <v>-7.769431092054322</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.225292710912453</v>
       </c>
       <c r="E19">
-        <v>-15.5442245886845</v>
+        <v>-16.43565922556842</v>
       </c>
       <c r="F19">
-        <v>-1.127928667652627</v>
+        <v>-1.635732883496878</v>
       </c>
       <c r="G19">
-        <v>-6.661136588053732</v>
+        <v>-7.656849369900327</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-2.421753663669225</v>
       </c>
       <c r="E20">
-        <v>-16.01937019546531</v>
+        <v>-18.08169160024648</v>
       </c>
       <c r="F20">
-        <v>-0.7786858799151318</v>
+        <v>-1.154544429267503</v>
       </c>
       <c r="G20">
-        <v>-6.810190590413878</v>
+        <v>-7.691103584595166</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-2.766660045774928</v>
       </c>
       <c r="E21">
-        <v>-15.98579608917244</v>
+        <v>-17.09067129145988</v>
       </c>
       <c r="F21">
-        <v>-0.6575181240307751</v>
+        <v>-0.9132597063736834</v>
       </c>
       <c r="G21">
-        <v>-7.080519807514145</v>
+        <v>-8.311933500120231</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-3.219835012958861</v>
       </c>
       <c r="E22">
-        <v>-17.2699218781055</v>
+        <v>-19.03018953810105</v>
       </c>
       <c r="F22">
-        <v>-0.3544118570218616</v>
+        <v>-0.7107536065253144</v>
       </c>
       <c r="G22">
-        <v>-6.871544930893191</v>
+        <v>-7.717952108918656</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-3.737409463072305</v>
       </c>
       <c r="E23">
-        <v>-17.66059785922123</v>
+        <v>-18.24367058702684</v>
       </c>
       <c r="F23">
-        <v>-0.1277811649636035</v>
+        <v>-0.4793710048677803</v>
       </c>
       <c r="G23">
-        <v>-6.857048051976722</v>
+        <v>-7.639627912005039</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-4.273859292064078</v>
       </c>
       <c r="E24">
-        <v>-17.08721153731802</v>
+        <v>-18.64709422247416</v>
       </c>
       <c r="F24">
-        <v>-0.03021458648408315</v>
+        <v>-0.5004920988090384</v>
       </c>
       <c r="G24">
-        <v>-6.875487790630463</v>
+        <v>-7.990102126065522</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-4.783724652668446</v>
       </c>
       <c r="E25">
-        <v>-18.26533480667954</v>
+        <v>-19.52746579735734</v>
       </c>
       <c r="F25">
-        <v>-0.05909108829324831</v>
+        <v>-0.6890322880421047</v>
       </c>
       <c r="G25">
-        <v>-7.138427870087077</v>
+        <v>-7.417937229967744</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.228440289746201</v>
       </c>
       <c r="E26">
-        <v>-17.52149672312762</v>
+        <v>-19.27651135327427</v>
       </c>
       <c r="F26">
-        <v>-0.01518600919952051</v>
+        <v>-0.3846281740354885</v>
       </c>
       <c r="G26">
-        <v>-7.887342792526544</v>
+        <v>-7.985202518667401</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.57670689181431</v>
       </c>
       <c r="E27">
-        <v>-17.63819549830528</v>
+        <v>-19.57670389524274</v>
       </c>
       <c r="F27">
-        <v>-0.2340407052129709</v>
+        <v>-0.5332075037572288</v>
       </c>
       <c r="G27">
-        <v>-7.519276339470374</v>
+        <v>-8.228213113977603</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.808792582540531</v>
       </c>
       <c r="E28">
-        <v>-17.54961854671525</v>
+        <v>-19.69336644262835</v>
       </c>
       <c r="F28">
-        <v>-0.102671507674311</v>
+        <v>-0.5022579309047535</v>
       </c>
       <c r="G28">
-        <v>-8.746243969417218</v>
+        <v>-8.899002472235809</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-5.915686212678341</v>
       </c>
       <c r="E29">
-        <v>-17.50216919606288</v>
+        <v>-18.52812668181866</v>
       </c>
       <c r="F29">
-        <v>-0.0824000719566861</v>
+        <v>-0.6193999063520631</v>
       </c>
       <c r="G29">
-        <v>-8.154278700449058</v>
+        <v>-8.389483029377658</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.900352825029199</v>
       </c>
       <c r="E30">
-        <v>-17.2834439014924</v>
+        <v>-19.18636302120358</v>
       </c>
       <c r="F30">
-        <v>0.03458670031091044</v>
+        <v>-0.1458805480182032</v>
       </c>
       <c r="G30">
-        <v>-8.3368751502131</v>
+        <v>-8.931492166158217</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.777258485678709</v>
       </c>
       <c r="E31">
-        <v>-17.67896534979634</v>
+        <v>-18.16556799581655</v>
       </c>
       <c r="F31">
-        <v>-0.1638944109533692</v>
+        <v>-0.5070407227693806</v>
       </c>
       <c r="G31">
-        <v>-8.18802309113085</v>
+        <v>-8.965577543030552</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.56841792245216</v>
       </c>
       <c r="E32">
-        <v>-17.07242606968298</v>
+        <v>-17.62166203970328</v>
       </c>
       <c r="F32">
-        <v>0.08553135219876659</v>
+        <v>-0.2753271265755196</v>
       </c>
       <c r="G32">
-        <v>-8.199222666690204</v>
+        <v>-8.585301798025549</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.300364407332987</v>
       </c>
       <c r="E33">
-        <v>-16.05881773254612</v>
+        <v>-17.21776291448515</v>
       </c>
       <c r="F33">
-        <v>-0.1104356259247529</v>
+        <v>-0.427742983877412</v>
       </c>
       <c r="G33">
-        <v>-7.849675405380717</v>
+        <v>-8.77599253163311</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.000262648511042</v>
       </c>
       <c r="E34">
-        <v>-16.93291284245467</v>
+        <v>-16.96187243373372</v>
       </c>
       <c r="F34">
-        <v>-0.4307868666468866</v>
+        <v>-0.4450243828266873</v>
       </c>
       <c r="G34">
-        <v>-7.708685891954236</v>
+        <v>-8.516604667540133</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.695486371580589</v>
       </c>
       <c r="E35">
-        <v>-15.82646173121256</v>
+        <v>-17.16379708973574</v>
       </c>
       <c r="F35">
-        <v>-0.03767146578692979</v>
+        <v>-0.6408171532995084</v>
       </c>
       <c r="G35">
-        <v>-6.726311298085364</v>
+        <v>-8.933879069492031</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.408609895553297</v>
       </c>
       <c r="E36">
-        <v>-15.42184257862721</v>
+        <v>-16.89887230333902</v>
       </c>
       <c r="F36">
-        <v>0.06102667056917201</v>
+        <v>-0.4207825963790556</v>
       </c>
       <c r="G36">
-        <v>-6.704541150619117</v>
+        <v>-7.734921965352959</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.160710827571187</v>
       </c>
       <c r="E37">
-        <v>-15.20939827750537</v>
+        <v>-16.21120993985225</v>
       </c>
       <c r="F37">
-        <v>-0.2009895546107074</v>
+        <v>-0.4635790813319758</v>
       </c>
       <c r="G37">
-        <v>-6.5131121653563</v>
+        <v>-7.144565621516886</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.968202116784841</v>
       </c>
       <c r="E38">
-        <v>-14.33883990579682</v>
+        <v>-15.608279853523</v>
       </c>
       <c r="F38">
-        <v>-0.1019113288349001</v>
+        <v>-0.5029618881841663</v>
       </c>
       <c r="G38">
-        <v>-6.594362884526633</v>
+        <v>-7.634791204972164</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.841692383474254</v>
       </c>
       <c r="E39">
-        <v>-13.75685854022705</v>
+        <v>-15.64055881624967</v>
       </c>
       <c r="F39">
-        <v>-0.3938825595523589</v>
+        <v>-0.3485339325167081</v>
       </c>
       <c r="G39">
-        <v>-6.460203026547668</v>
+        <v>-7.404142186705601</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.786643710242919</v>
       </c>
       <c r="E40">
-        <v>-13.49625844650764</v>
+        <v>-14.43678174163471</v>
       </c>
       <c r="F40">
-        <v>-0.1611102559540266</v>
+        <v>-0.6566359998358754</v>
       </c>
       <c r="G40">
-        <v>-6.67958956888963</v>
+        <v>-6.302703822516841</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.800774814164177</v>
       </c>
       <c r="E41">
-        <v>-13.32436210165049</v>
+        <v>-15.01956011862982</v>
       </c>
       <c r="F41">
-        <v>-0.1392598654387086</v>
+        <v>-0.416902516886229</v>
       </c>
       <c r="G41">
-        <v>-6.478298468465324</v>
+        <v>-5.940811536891411</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.87554862338892</v>
       </c>
       <c r="E42">
-        <v>-13.83370674413722</v>
+        <v>-14.68145066379513</v>
       </c>
       <c r="F42">
-        <v>-0.1740744725778139</v>
+        <v>-0.7430129041698582</v>
       </c>
       <c r="G42">
-        <v>-6.361949345487638</v>
+        <v>-6.284995714427279</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.994056308964042</v>
       </c>
       <c r="E43">
-        <v>-13.05873993025657</v>
+        <v>-14.73163521274813</v>
       </c>
       <c r="F43">
-        <v>-0.3746048992966722</v>
+        <v>-0.7506542852118536</v>
       </c>
       <c r="G43">
-        <v>-5.853532314294066</v>
+        <v>-7.012623829049232</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.135942983901182</v>
       </c>
       <c r="E44">
-        <v>-11.80651271223354</v>
+        <v>-13.33317904054342</v>
       </c>
       <c r="F44">
-        <v>-0.247310577078438</v>
+        <v>-1.037407204937939</v>
       </c>
       <c r="G44">
-        <v>-5.690825622129966</v>
+        <v>-6.624747071486063</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.278658815954479</v>
       </c>
       <c r="E45">
-        <v>-11.54105809437791</v>
+        <v>-12.77635334808627</v>
       </c>
       <c r="F45">
-        <v>-0.3565538192724934</v>
+        <v>-0.8873265220083625</v>
       </c>
       <c r="G45">
-        <v>-5.723715892062624</v>
+        <v>-6.323702612872438</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.401182341587629</v>
       </c>
       <c r="E46">
-        <v>-11.43025539235824</v>
+        <v>-11.41905647613727</v>
       </c>
       <c r="F46">
-        <v>-0.9278868142086821</v>
+        <v>-0.9771954978858893</v>
       </c>
       <c r="G46">
-        <v>-6.192806952795195</v>
+        <v>-6.626134190067018</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.4850614368196</v>
       </c>
       <c r="E47">
-        <v>-11.58730287094424</v>
+        <v>-12.43405958326849</v>
       </c>
       <c r="F47">
-        <v>-0.6566676739541841</v>
+        <v>-1.35717247447136</v>
       </c>
       <c r="G47">
-        <v>-6.053628307778695</v>
+        <v>-6.478910919390089</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.5181368427953</v>
       </c>
       <c r="E48">
-        <v>-10.29416994720993</v>
+        <v>-11.65259440918684</v>
       </c>
       <c r="F48">
-        <v>-0.6533125929723257</v>
+        <v>-1.177573888836865</v>
       </c>
       <c r="G48">
-        <v>-5.687882547145553</v>
+        <v>-6.210789836164516</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.499023303347941</v>
       </c>
       <c r="E49">
-        <v>-9.708081255715207</v>
+        <v>-11.39411816977703</v>
       </c>
       <c r="F49">
-        <v>-0.7634886379505749</v>
+        <v>-1.36731611085975</v>
       </c>
       <c r="G49">
-        <v>-5.312943401549855</v>
+        <v>-7.281450058474671</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.433699860365006</v>
       </c>
       <c r="E50">
-        <v>-9.904562685960009</v>
+        <v>-10.0205686046145</v>
       </c>
       <c r="F50">
-        <v>-1.031987763295306</v>
+        <v>-1.681556622307161</v>
       </c>
       <c r="G50">
-        <v>-5.809194177886607</v>
+        <v>-6.810005199863679</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.336761642178737</v>
       </c>
       <c r="E51">
-        <v>-8.391803301327688</v>
+        <v>-12.34655588001827</v>
       </c>
       <c r="F51">
-        <v>-1.090985559763171</v>
+        <v>-1.873798724117567</v>
       </c>
       <c r="G51">
-        <v>-5.121511105741499</v>
+        <v>-5.44878501666277</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.227335337829146</v>
       </c>
       <c r="E52">
-        <v>-8.658829299663978</v>
+        <v>-10.96788008227906</v>
       </c>
       <c r="F52">
-        <v>-1.207650047876976</v>
+        <v>-1.293169375457748</v>
       </c>
       <c r="G52">
-        <v>-5.010869363273517</v>
+        <v>-6.159559143944294</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.127768435159084</v>
       </c>
       <c r="E53">
-        <v>-8.954103918860115</v>
+        <v>-11.47217094777323</v>
       </c>
       <c r="F53">
-        <v>-1.2674333624789</v>
+        <v>-1.430539234710008</v>
       </c>
       <c r="G53">
-        <v>-5.344466416174796</v>
+        <v>-4.881873956335815</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.061652633461025</v>
       </c>
       <c r="E54">
-        <v>-8.277835195976648</v>
+        <v>-8.969038826137412</v>
       </c>
       <c r="F54">
-        <v>-1.545502030817673</v>
+        <v>-1.544429861912921</v>
       </c>
       <c r="G54">
-        <v>-5.84674238539302</v>
+        <v>-6.873021434203706</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.050761870256362</v>
       </c>
       <c r="E55">
-        <v>-7.964179500783375</v>
+        <v>-9.021668751054557</v>
       </c>
       <c r="F55">
-        <v>-1.369662371173474</v>
+        <v>-1.92149044405511</v>
       </c>
       <c r="G55">
-        <v>-5.452386890209497</v>
+        <v>-5.926466943069749</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.11198179635784</v>
       </c>
       <c r="E56">
-        <v>-8.254767149381575</v>
+        <v>-9.644845644672097</v>
       </c>
       <c r="F56">
-        <v>-1.265646942206284</v>
+        <v>-1.437816363391453</v>
       </c>
       <c r="G56">
-        <v>-5.334627474832081</v>
+        <v>-6.057246734053118</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.251567559029508</v>
       </c>
       <c r="E57">
-        <v>-7.460178457625696</v>
+        <v>-9.12169368493598</v>
       </c>
       <c r="F57">
-        <v>-1.331727863380953</v>
+        <v>-2.361067025356314</v>
       </c>
       <c r="G57">
-        <v>-5.608975694217024</v>
+        <v>-6.325397612188545</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.467905819191101</v>
       </c>
       <c r="E58">
-        <v>-7.719075845118217</v>
+        <v>-8.632546036523459</v>
       </c>
       <c r="F58">
-        <v>-1.806542693153642</v>
+        <v>-2.015232372748844</v>
       </c>
       <c r="G58">
-        <v>-6.437456268147336</v>
+        <v>-6.707894733250399</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.748930782389209</v>
       </c>
       <c r="E59">
-        <v>-7.192115438741649</v>
+        <v>-7.481652481370068</v>
       </c>
       <c r="F59">
-        <v>-1.292695847389032</v>
+        <v>-2.064522051955066</v>
       </c>
       <c r="G59">
-        <v>-5.245130186723425</v>
+        <v>-5.679146017467416</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.081822952497225</v>
       </c>
       <c r="E60">
-        <v>-7.213951740406634</v>
+        <v>-8.356313650529575</v>
       </c>
       <c r="F60">
-        <v>-1.915151661128564</v>
+        <v>-1.83956454519647</v>
       </c>
       <c r="G60">
-        <v>-5.393426074155077</v>
+        <v>-5.8888988722901</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.453324606166309</v>
       </c>
       <c r="E61">
-        <v>-6.651791505568444</v>
+        <v>-7.716059881429109</v>
       </c>
       <c r="F61">
-        <v>-1.585677482480541</v>
+        <v>-2.146611864375954</v>
       </c>
       <c r="G61">
-        <v>-5.555917580859125</v>
+        <v>-6.523136497249213</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.84838517678359</v>
       </c>
       <c r="E62">
-        <v>-6.519551007596455</v>
+        <v>-7.472636289620796</v>
       </c>
       <c r="F62">
-        <v>-1.737873204660187</v>
+        <v>-1.7065736328004</v>
       </c>
       <c r="G62">
-        <v>-6.27785817824461</v>
+        <v>-6.88790233640273</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.253600375320851</v>
       </c>
       <c r="E63">
-        <v>-6.133131792047935</v>
+        <v>-8.003993844258813</v>
       </c>
       <c r="F63">
-        <v>-1.638273147785243</v>
+        <v>-2.267568987373558</v>
       </c>
       <c r="G63">
-        <v>-5.522653219280528</v>
+        <v>-6.518025014936578</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.654143658215179</v>
       </c>
       <c r="E64">
-        <v>-6.387772413973247</v>
+        <v>-7.102456181863783</v>
       </c>
       <c r="F64">
-        <v>-1.542676699464529</v>
+        <v>-1.9338496850192</v>
       </c>
       <c r="G64">
-        <v>-6.078970533881815</v>
+        <v>-7.276517345621157</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.039317514107933</v>
       </c>
       <c r="E65">
-        <v>-5.784425708035295</v>
+        <v>-7.958011719184928</v>
       </c>
       <c r="F65">
-        <v>-1.699346390855292</v>
+        <v>-2.064012098650295</v>
       </c>
       <c r="G65">
-        <v>-6.23461583241065</v>
+        <v>-7.352921426121997</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.401052754922504</v>
       </c>
       <c r="E66">
-        <v>-6.927000456436595</v>
+        <v>-7.614463567067024</v>
       </c>
       <c r="F66">
-        <v>-1.818380894871552</v>
+        <v>-2.390843072125449</v>
       </c>
       <c r="G66">
-        <v>-6.519465102246161</v>
+        <v>-6.305835598596992</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.737542198306022</v>
       </c>
       <c r="E67">
-        <v>-6.738837832943884</v>
+        <v>-7.056809163866466</v>
       </c>
       <c r="F67">
-        <v>-1.809955579401414</v>
+        <v>-1.9524004242597</v>
       </c>
       <c r="G67">
-        <v>-6.229828783560865</v>
+        <v>-7.244001167334435</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.049590248889468</v>
       </c>
       <c r="E68">
-        <v>-6.975074736502023</v>
+        <v>-8.19422598037303</v>
       </c>
       <c r="F68">
-        <v>-1.99245709797891</v>
+        <v>-2.363348353727505</v>
       </c>
       <c r="G68">
-        <v>-6.265016572097777</v>
+        <v>-7.197117221407277</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.340507318147734</v>
       </c>
       <c r="E69">
-        <v>-6.126773814541166</v>
+        <v>-6.954995482752013</v>
       </c>
       <c r="F69">
-        <v>-1.781021272326335</v>
+        <v>-2.232800307706</v>
       </c>
       <c r="G69">
-        <v>-6.358794395588713</v>
+        <v>-6.888481681872102</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.613519154976601</v>
       </c>
       <c r="E70">
-        <v>-5.810672743383752</v>
+        <v>-7.395326181361848</v>
       </c>
       <c r="F70">
-        <v>-1.649266442397266</v>
+        <v>-2.125124142515272</v>
       </c>
       <c r="G70">
-        <v>-6.290481288385852</v>
+        <v>-7.226779709439146</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.86859978901734</v>
       </c>
       <c r="E71">
-        <v>-6.54595653953518</v>
+        <v>-7.123490943629411</v>
       </c>
       <c r="F71">
-        <v>-1.747353268270008</v>
+        <v>-2.231653704623222</v>
       </c>
       <c r="G71">
-        <v>-6.390711365132826</v>
+        <v>-7.479900710826282</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-9.108678869694392</v>
       </c>
       <c r="E72">
-        <v>-6.864756581201166</v>
+        <v>-8.426862747095072</v>
       </c>
       <c r="F72">
-        <v>-1.896641306388908</v>
+        <v>-2.507858351099523</v>
       </c>
       <c r="G72">
-        <v>-6.166014707745873</v>
+        <v>-7.113764305819506</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-9.333118063878448</v>
       </c>
       <c r="E73">
-        <v>-6.355593077674741</v>
+        <v>-7.623583913718472</v>
       </c>
       <c r="F73">
-        <v>-2.171110211181887</v>
+        <v>-2.576766187333251</v>
       </c>
       <c r="G73">
-        <v>-6.497721439144228</v>
+        <v>-7.593621260645786</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-9.545057812666286</v>
       </c>
       <c r="E74">
-        <v>-6.072056263106485</v>
+        <v>-9.018439949087089</v>
       </c>
       <c r="F74">
-        <v>-1.953963541998238</v>
+        <v>-2.528093361581093</v>
       </c>
       <c r="G74">
-        <v>-6.152547408492118</v>
+        <v>-6.98774507932161</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-9.748012406189055</v>
       </c>
       <c r="E75">
-        <v>-6.938317112981763</v>
+        <v>-9.885579322919854</v>
       </c>
       <c r="F75">
-        <v>-2.001136598248475</v>
+        <v>-2.815004651898723</v>
       </c>
       <c r="G75">
-        <v>-5.707894794930447</v>
+        <v>-7.390976147095919</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-9.944018339322666</v>
       </c>
       <c r="E76">
-        <v>-8.269923951885247</v>
+        <v>-10.31685760198836</v>
       </c>
       <c r="F76">
-        <v>-2.505705302907483</v>
+        <v>-2.78353324794711</v>
       </c>
       <c r="G76">
-        <v>-6.365081121567789</v>
+        <v>-7.267817231943952</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.1276414786941</v>
       </c>
       <c r="E77">
-        <v>-7.750584967263587</v>
+        <v>-10.41467716902804</v>
       </c>
       <c r="F77">
-        <v>-2.585136864949307</v>
+        <v>-2.545404850942762</v>
       </c>
       <c r="G77">
-        <v>-6.137395041558873</v>
+        <v>-6.969503973400226</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.28733830951745</v>
       </c>
       <c r="E78">
-        <v>-8.247159313048687</v>
+        <v>-9.518265739209696</v>
       </c>
       <c r="F78">
-        <v>-2.305033926362151</v>
+        <v>-2.502565605930125</v>
       </c>
       <c r="G78">
-        <v>-6.212282892202727</v>
+        <v>-7.146654575752166</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.41047795469993</v>
       </c>
       <c r="E79">
-        <v>-8.816465479870983</v>
+        <v>-9.580844721521693</v>
       </c>
       <c r="F79">
-        <v>-2.479427662505554</v>
+        <v>-2.604199141200493</v>
       </c>
       <c r="G79">
-        <v>-6.491742593900304</v>
+        <v>-7.162906043804449</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.48469241779758</v>
       </c>
       <c r="E80">
-        <v>-9.520593374849639</v>
+        <v>-11.10804540976448</v>
       </c>
       <c r="F80">
-        <v>-2.42483969515923</v>
+        <v>-3.02537701902908</v>
       </c>
       <c r="G80">
-        <v>-5.963518568745272</v>
+        <v>-6.737643295466289</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.50427871648902</v>
       </c>
       <c r="E81">
-        <v>-10.48296202858971</v>
+        <v>-11.02665061795061</v>
       </c>
       <c r="F81">
-        <v>-2.673966929746305</v>
+        <v>-3.033509348904861</v>
       </c>
       <c r="G81">
-        <v>-6.17075209841257</v>
+        <v>-7.706679701357437</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.46431556985777</v>
       </c>
       <c r="E82">
-        <v>-10.46766484339179</v>
+        <v>-11.71727007496438</v>
       </c>
       <c r="F82">
-        <v>-2.490919032627983</v>
+        <v>-3.089298557188047</v>
       </c>
       <c r="G82">
-        <v>-5.882380408123274</v>
+        <v>-6.901823180395366</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.36848501157734</v>
       </c>
       <c r="E83">
-        <v>-11.97973589997495</v>
+        <v>-13.68643171245976</v>
       </c>
       <c r="F83">
-        <v>-2.556871673623501</v>
+        <v>-3.017985071668766</v>
       </c>
       <c r="G83">
-        <v>-5.89984353584293</v>
+        <v>-6.986172570190456</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-10.22390097000049</v>
       </c>
       <c r="E84">
-        <v>-12.6494428640213</v>
+        <v>-14.48232913320386</v>
       </c>
       <c r="F84">
-        <v>-2.708043529928816</v>
+        <v>-2.999733652846284</v>
       </c>
       <c r="G84">
-        <v>-6.1825144667136</v>
+        <v>-7.319865628912374</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-10.04065302793913</v>
       </c>
       <c r="E85">
-        <v>-14.26805532858292</v>
+        <v>-15.57664846257942</v>
       </c>
       <c r="F85">
-        <v>-2.96445660357987</v>
+        <v>-3.07466036341164</v>
       </c>
       <c r="G85">
-        <v>-6.661020718959858</v>
+        <v>-6.571692268673703</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.833121967009342</v>
       </c>
       <c r="E86">
-        <v>-13.54813664473952</v>
+        <v>-15.95996567343269</v>
       </c>
       <c r="F86">
-        <v>-2.911267048556879</v>
+        <v>-3.086325149331809</v>
       </c>
       <c r="G86">
-        <v>-6.110483616870138</v>
+        <v>-7.364256734048461</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.616328420361716</v>
       </c>
       <c r="E87">
-        <v>-15.74362235619024</v>
+        <v>-17.46642595072034</v>
       </c>
       <c r="F87">
-        <v>-3.318988969074934</v>
+        <v>-3.298394457350559</v>
       </c>
       <c r="G87">
-        <v>-6.467244556909697</v>
+        <v>-6.999365094164451</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.407364886390724</v>
       </c>
       <c r="E88">
-        <v>-17.53829283322207</v>
+        <v>-19.27815066086505</v>
       </c>
       <c r="F88">
-        <v>-2.996795878373144</v>
+        <v>-3.225022945994165</v>
       </c>
       <c r="G88">
-        <v>-5.594839664764336</v>
+        <v>-6.950829186013197</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.220331916085859</v>
       </c>
       <c r="E89">
-        <v>-19.02053935999071</v>
+        <v>-19.80077731761628</v>
       </c>
       <c r="F89">
-        <v>-3.088927970003834</v>
+        <v>-3.522970290983535</v>
       </c>
       <c r="G89">
-        <v>-6.03702261135371</v>
+        <v>-6.510662361657239</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.070560754583777</v>
       </c>
       <c r="E90">
-        <v>-20.57265571222369</v>
+        <v>-20.99045725264537</v>
       </c>
       <c r="F90">
-        <v>-3.395075744223349</v>
+        <v>-3.479924372348933</v>
       </c>
       <c r="G90">
-        <v>-5.557188830346205</v>
+        <v>-7.159840478635084</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-8.967995122858698</v>
       </c>
       <c r="E91">
-        <v>-22.41643296139469</v>
+        <v>-23.81007083725525</v>
       </c>
       <c r="F91">
-        <v>-3.101451916383129</v>
+        <v>-3.388410717878222</v>
       </c>
       <c r="G91">
-        <v>-5.874345714099463</v>
+        <v>-6.347243902202195</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.922811375858027</v>
       </c>
       <c r="E92">
-        <v>-24.30674480946852</v>
+        <v>-25.15672579528622</v>
       </c>
       <c r="F92">
-        <v>-3.102010172718321</v>
+        <v>-3.506250315781283</v>
       </c>
       <c r="G92">
-        <v>-6.228428422797752</v>
+        <v>-6.933574622662515</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.93948313236603</v>
       </c>
       <c r="E93">
-        <v>-26.44360489641594</v>
+        <v>-28.05855835397936</v>
       </c>
       <c r="F93">
-        <v>-3.331969814610833</v>
+        <v>-3.37979931696302</v>
       </c>
       <c r="G93">
-        <v>-7.235966473310624</v>
+        <v>-6.410349521271783</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.015501226616774</v>
       </c>
       <c r="E94">
-        <v>-28.47694406754802</v>
+        <v>-28.73037558691329</v>
       </c>
       <c r="F94">
-        <v>-3.18422826531836</v>
+        <v>-3.406370734812263</v>
       </c>
       <c r="G94">
-        <v>-6.539106568930657</v>
+        <v>-6.892844980892862</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.147170735741772</v>
       </c>
       <c r="E95">
-        <v>-31.09332879564167</v>
+        <v>-32.24329627786049</v>
       </c>
       <c r="F95">
-        <v>-3.033064327542623</v>
+        <v>-3.531098661594528</v>
       </c>
       <c r="G95">
-        <v>-6.545366810545419</v>
+        <v>-7.971788188142273</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.323440623176712</v>
       </c>
       <c r="E96">
-        <v>-33.38765071654681</v>
+        <v>-34.58662081600263</v>
       </c>
       <c r="F96">
-        <v>-2.992132656305133</v>
+        <v>-3.503487540811799</v>
       </c>
       <c r="G96">
-        <v>-6.893659375095523</v>
+        <v>-7.416013803009426</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.526088831531446</v>
       </c>
       <c r="E97">
-        <v>-35.43495796575555</v>
+        <v>-36.63646853912968</v>
       </c>
       <c r="F97">
-        <v>-3.099557804108263</v>
+        <v>-3.568432944845097</v>
       </c>
       <c r="G97">
-        <v>-6.782537603524346</v>
+        <v>-7.765253183583762</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-9.739695943899894</v>
       </c>
       <c r="E98">
-        <v>-39.31266988039064</v>
+        <v>-39.12297663268334</v>
       </c>
       <c r="F98">
-        <v>-2.852802960982516</v>
+        <v>-3.201504913149889</v>
       </c>
       <c r="G98">
-        <v>-7.361571881616112</v>
+        <v>-7.321997620239665</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-9.945653838306146</v>
       </c>
       <c r="E99">
-        <v>-40.92728370240349</v>
+        <v>-41.80338719053444</v>
       </c>
       <c r="F99">
-        <v>-3.221199088061336</v>
+        <v>-3.190657319482087</v>
       </c>
       <c r="G99">
-        <v>-7.80982305817897</v>
+        <v>-9.358986222189843</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.14917617471089</v>
       </c>
       <c r="E100">
-        <v>-43.61106118067929</v>
+        <v>-44.57590917393855</v>
       </c>
       <c r="F100">
-        <v>-2.696061210972601</v>
+        <v>-3.111903583572071</v>
       </c>
       <c r="G100">
-        <v>-8.142953324159212</v>
+        <v>-8.508152844778374</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.33822485342115</v>
       </c>
       <c r="E101">
-        <v>-45.94507064778765</v>
+        <v>-47.35486838314457</v>
       </c>
       <c r="F101">
-        <v>-3.100260177681761</v>
+        <v>-2.97792364683181</v>
       </c>
       <c r="G101">
-        <v>-9.177932486647103</v>
+        <v>-9.324036792931757</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.54916305629826</v>
       </c>
       <c r="E102">
-        <v>-48.71077161721771</v>
+        <v>-50.60107440834351</v>
       </c>
       <c r="F102">
-        <v>-2.798254586284078</v>
+        <v>-3.242187150705698</v>
       </c>
       <c r="G102">
-        <v>-9.282800637694596</v>
+        <v>-9.541817720687174</v>
       </c>
     </row>
   </sheetData>
